--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.55295053372309</v>
+        <v>7.727354461730003</v>
       </c>
       <c r="D2" t="n">
-        <v>37.80198539708667</v>
+        <v>6.142822627026583</v>
       </c>
       <c r="E2" t="n">
-        <v>13.15985317449473</v>
+        <v>2.138476140855393</v>
       </c>
       <c r="F2" t="n">
-        <v>11.33106150485498</v>
+        <v>1.841297494538934</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.06604819383315</v>
+        <v>4.398232831497887</v>
       </c>
       <c r="D3" t="n">
-        <v>26.09202984687433</v>
+        <v>4.239954850117079</v>
       </c>
       <c r="E3" t="n">
-        <v>13.15985317449473</v>
+        <v>2.138476140855393</v>
       </c>
       <c r="F3" t="n">
-        <v>11.33106150485498</v>
+        <v>1.841297494538934</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.19511780109997</v>
+        <v>8.806706642678746</v>
       </c>
       <c r="D4" t="n">
-        <v>25.95754267125801</v>
+        <v>4.218100684079427</v>
       </c>
       <c r="E4" t="n">
-        <v>13.15985317449473</v>
+        <v>2.138476140855393</v>
       </c>
       <c r="F4" t="n">
-        <v>11.33106150485498</v>
+        <v>1.841297494538934</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.74064690756899</v>
+        <v>5.645355122479961</v>
       </c>
       <c r="D5" t="n">
-        <v>31.17335921397702</v>
+        <v>5.065670872271267</v>
       </c>
       <c r="E5" t="n">
-        <v>13.15985317449473</v>
+        <v>2.138476140855393</v>
       </c>
       <c r="F5" t="n">
-        <v>11.33106150485498</v>
+        <v>1.841297494538934</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>11.63390348200492</v>
+        <v>1.890509315825799</v>
       </c>
       <c r="D6" t="n">
-        <v>12.47125177051016</v>
+        <v>2.026578412707901</v>
       </c>
       <c r="E6" t="n">
-        <v>13.15985317449473</v>
+        <v>2.138476140855393</v>
       </c>
       <c r="F6" t="n">
-        <v>11.33106150485498</v>
+        <v>1.841297494538934</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.85047527013658</v>
+        <v>8.588202231397194</v>
       </c>
       <c r="D7" t="n">
-        <v>43.50647801619107</v>
+        <v>7.06980267763105</v>
       </c>
       <c r="E7" t="n">
-        <v>13.15985317449473</v>
+        <v>2.138476140855393</v>
       </c>
       <c r="F7" t="n">
-        <v>11.33106150485498</v>
+        <v>1.841297494538934</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.29633388491018</v>
+        <v>7.035654256297905</v>
       </c>
       <c r="D8" t="n">
-        <v>44.28237956929625</v>
+        <v>7.19588668001064</v>
       </c>
       <c r="E8" t="n">
-        <v>13.15985317449473</v>
+        <v>2.138476140855393</v>
       </c>
       <c r="F8" t="n">
-        <v>11.33106150485498</v>
+        <v>1.841297494538934</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>44.41985708047908</v>
+        <v>7.218226775577851</v>
       </c>
       <c r="D9" t="n">
-        <v>43.67260006901218</v>
+        <v>7.09679751121448</v>
       </c>
       <c r="E9" t="n">
-        <v>13.15985317449473</v>
+        <v>2.138476140855393</v>
       </c>
       <c r="F9" t="n">
-        <v>11.33106150485498</v>
+        <v>1.841297494538934</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>50.45226127017377</v>
+        <v>8.198492456403239</v>
       </c>
       <c r="D10" t="n">
-        <v>50.18701491073261</v>
+        <v>8.155389922994049</v>
       </c>
       <c r="E10" t="n">
-        <v>13.15985317449473</v>
+        <v>2.138476140855393</v>
       </c>
       <c r="F10" t="n">
-        <v>11.33106150485498</v>
+        <v>1.841297494538934</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
